--- a/artfynd/A 42957-2025 artfynd.xlsx
+++ b/artfynd/A 42957-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,16 +678,11 @@
         <v>15545013</v>
       </c>
       <c r="B2" t="n">
-        <v>44335</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>45049</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -734,10 +729,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>483913.933789316</v>
+        <v>483914</v>
       </c>
       <c r="R2" t="n">
-        <v>6238905.505536723</v>
+        <v>6238906</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -811,58 +806,67 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>72275797</v>
+        <v>60494266</v>
       </c>
       <c r="B3" t="n">
-        <v>106964</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>45049</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220299</v>
+        <v>102021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Mindre bastardsvärmare</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Zygaena viciae</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Denis &amp; Schiffermüller, 1775)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Åkeholm 4055/1255, Bl</t>
+          <t>Åkeholm 1250/4050, Bl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>483918.9565125387</v>
+        <v>483944</v>
       </c>
       <c r="R3" t="n">
-        <v>6238910.480175494</v>
+        <v>6238891</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -886,34 +890,34 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2017-06-03</t>
+          <t>2016-07-08</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2017-06-03</t>
+          <t>2016-07-08</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Vägren</t>
+          <t>På Knautia</t>
         </is>
       </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG3" t="b">
         <v>0</v>
@@ -930,6 +934,113 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>72275797</v>
+      </c>
+      <c r="B4" t="n">
+        <v>110078</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Åkeholm 4055/1255, Bl</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>483919</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6238910</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Karlshamn</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Asarum</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2017-06-03</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2017-06-03</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Vägren</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Gunnar Hallin</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Gunnar Hallin</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
